--- a/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
+++ b/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE4D86B-0F7E-42AF-B590-E207538D49A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44039FB8-8353-49FD-A772-458A81CDCB68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
   </bookViews>
   <sheets>
     <sheet name="MEIAS" sheetId="1" r:id="rId1"/>
     <sheet name="MARCENARIA" sheetId="3" r:id="rId2"/>
+    <sheet name="FABRICA DE BRINQUEDOS" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>Função Objetivo</t>
   </si>
@@ -48,15 +49,66 @@
   <si>
     <t>Armario</t>
   </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>R1 = Plastico</t>
+  </si>
+  <si>
+    <t>R2 = M.O.</t>
+  </si>
+  <si>
+    <t>VARIÁVEIS</t>
+  </si>
+  <si>
+    <t>B1= QTD. DE BRINQUEDOS A SER PRODUZIDA</t>
+  </si>
+  <si>
+    <t>B2= QTD. DE BRINQUEDOS A SER PRODUZIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Função Objetivo = Max(Lucro) </t>
+  </si>
+  <si>
+    <t>8*B1+5*B2</t>
+  </si>
+  <si>
+    <t>RESTRIÇÕES</t>
+  </si>
+  <si>
+    <t>PLASTICO</t>
+  </si>
+  <si>
+    <t>MÃO DE OBRA</t>
+  </si>
+  <si>
+    <t>2*B1+1B2 &lt;=1000 KG</t>
+  </si>
+  <si>
+    <t>MKT</t>
+  </si>
+  <si>
+    <t>B1+B2 &lt;=700</t>
+  </si>
+  <si>
+    <t>3*B1+4*B2&lt;=2400MIN</t>
+  </si>
+  <si>
+    <t>2400=40H</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,8 +123,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -84,8 +158,23 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -93,35 +182,159 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="5"/>
+      </right>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
     <cellStyle name="Bom" xfId="1" builtinId="26"/>
+    <cellStyle name="Cálculo" xfId="4" builtinId="22"/>
+    <cellStyle name="Entrada" xfId="3" builtinId="20"/>
+    <cellStyle name="Neutro" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -139,14 +352,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF9999"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -193,27 +406,17 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -230,7 +433,26 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1275,6 +1497,531 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>BRINQUEDOS</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'FABRICA DE BRINQUEDOS'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>B2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'FABRICA DE BRINQUEDOS'!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'FABRICA DE BRINQUEDOS'!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7B2D-4E6C-A597-134514F272BD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="r"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="812372704"/>
+        <c:axId val="819850496"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="812372704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="800"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>B1</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="819850496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="30"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="819850496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>B2</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="812372704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="30"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1355,6 +2102,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1872,6 +2659,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2813,13 +4116,277 @@
 </c:userShapes>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>209551</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BF8F40C-1945-4EEF-BA43-53A750251C43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.06673</cdr:x>
+      <cdr:y>0.11556</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.63577</cdr:x>
+      <cdr:y>0.91111</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="5" name="Conector reto 4">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F198E37C-AED7-41C3-93D9-60888376F771}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="685800" y="742950"/>
+          <a:ext cx="5848350" cy="5114925"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.05561</cdr:x>
+      <cdr:y>0.61866</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.43129</cdr:x>
+      <cdr:y>0.91407</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="8" name="Retângulo 7">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{550D4823-7B28-4307-8AA8-6EA5F26D80B4}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="571500" y="3977613"/>
+          <a:ext cx="3861061" cy="1899311"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="wdDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="bg1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="tx2">
+              <a:alpha val="16000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.06506</cdr:x>
+      <cdr:y>0.43201</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.97868</cdr:x>
+      <cdr:y>0.90963</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="9" name="Conector reto 8">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FF22B94-90AB-4F3C-BCDC-110E3292018C}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="668610" y="2777579"/>
+          <a:ext cx="9389790" cy="3070771"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.06691</cdr:x>
+      <cdr:y>0.35628</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.86469</cdr:x>
+      <cdr:y>0.91407</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="17" name="Conector reto 16">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0DA861A-7626-43F8-A5F5-814BBB4A6B0A}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="687713" y="2290672"/>
+          <a:ext cx="8199112" cy="3586253"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B92EF86-C117-4AAB-83FC-A9F29285C342}" name="Tabela1" displayName="Tabela1" ref="A1:E6" totalsRowShown="0">
   <autoFilter ref="A1:E6" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{CD3C573B-0C34-40C3-BE2D-4CC62EED4169}" name="Kit A"/>
     <tableColumn id="2" xr3:uid="{233C09F4-EFE5-4067-8D0A-727EFB3A34C6}" name="Kit B"/>
-    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="19">
+    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="20">
       <calculatedColumnFormula>6*A2+8*B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{5E73BE8E-91D0-4391-B883-BB1694E2FB56}" name="R1 = Algodão">
@@ -2839,14 +4406,34 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{243F2FF8-6FFB-48E8-A0A8-9E27635C554E}" name="Mesa"/>
     <tableColumn id="2" xr3:uid="{936CC617-A79F-4905-94F7-13BFF79EEC6B}" name="Armario"/>
-    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="16">
+    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="19">
       <calculatedColumnFormula>4*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="15">
+    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="18">
       <calculatedColumnFormula>2*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="14">
+    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="17">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D4E9F9F4-33C9-4351-8E5E-FE895863D27C}" name="Tabela134" displayName="Tabela134" ref="A1:E7" totalsRowShown="0">
+  <autoFilter ref="A1:E7" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{7142BF79-17B1-4B0B-A34F-7AAA22690851}" name="B1"/>
+    <tableColumn id="2" xr3:uid="{253F461F-5BA1-4522-9AFC-63887ECB9A1D}" name="B2"/>
+    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="16">
+      <calculatedColumnFormula>8*A2+5*B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="11">
+      <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="10">
+      <calculatedColumnFormula>3*A2+4*B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3231,7 +4818,7 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E3:E6" si="2">4*A4+8*B4</f>
+        <f t="shared" ref="E4:E6" si="2">4*A4+8*B4</f>
         <v>84</v>
       </c>
     </row>
@@ -3277,12 +4864,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="lessThanOrEqual">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThanOrEqual">
       <formula>84</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3423,10 +5010,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThanOrEqual">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3446,4 +5033,250 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6E2673-FA2C-4936-AC92-6D9FE69529DB}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="1">
+        <f t="shared" ref="C2:C6" si="0">8*A2+5*B2</f>
+        <v>5000</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:D4" si="1">2*A2+1*B2</f>
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ref="E2:E6" si="2">3*A2+4*B2</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="13">
+        <v>500</v>
+      </c>
+      <c r="B3" s="14">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="2"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>0</v>
+      </c>
+      <c r="B4" s="12">
+        <v>600</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="2"/>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="13">
+        <v>800</v>
+      </c>
+      <c r="B5" s="14">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="0"/>
+        <v>6400</v>
+      </c>
+      <c r="D5">
+        <f>2*A5+1*B5</f>
+        <v>1600</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>700</v>
+      </c>
+      <c r="C6" s="1">
+        <f>8*A6+5*B6</f>
+        <v>3500</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D7" si="3">2*A6+1*B6</f>
+        <v>700</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>700</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <f>8*A7+5*B7</f>
+        <v>5600</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="3"/>
+        <v>1400</v>
+      </c>
+      <c r="E7" s="15">
+        <f>3*A7+4*B7</f>
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E8:E10 E14:E1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
+++ b/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44039FB8-8353-49FD-A772-458A81CDCB68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8757B584-31A5-4D35-8CC3-E150B2E3D745}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Função Objetivo</t>
   </si>
@@ -100,6 +100,9 @@
   <si>
     <t>2400=40H</t>
   </si>
+  <si>
+    <t>R3=MKT</t>
+  </si>
 </sst>
 </file>
 
@@ -146,7 +149,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,8 +176,26 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -194,43 +215,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="5"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="5"/>
-      </top>
-      <bottom style="thin">
-        <color theme="5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="5"/>
-      </top>
-      <bottom style="thin">
-        <color theme="5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="5"/>
-      </right>
-      <top style="thin">
-        <color theme="5"/>
-      </top>
-      <bottom style="thin">
-        <color theme="5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -301,18 +285,17 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
@@ -321,11 +304,18 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bom" xfId="1" builtinId="26"/>
@@ -334,7 +324,7 @@
     <cellStyle name="Neutro" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="36">
     <dxf>
       <fill>
         <patternFill>
@@ -358,8 +348,93 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -406,10 +481,26 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -438,6 +529,12 @@
           <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
@@ -1668,10 +1765,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'FABRICA DE BRINQUEDOS'!$A$2:$A$7</c:f>
+              <c:f>'FABRICA DE BRINQUEDOS'!$A$2:$A$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1690,15 +1787,18 @@
                 <c:pt idx="5">
                   <c:v>700</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>320</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FABRICA DE BRINQUEDOS'!$B$2:$B$7</c:f>
+              <c:f>'FABRICA DE BRINQUEDOS'!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -1716,6 +1816,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4120,16 +4223,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>209551</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>514351</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4214,10 +4317,10 @@
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
       <cdr:x>0.05561</cdr:x>
-      <cdr:y>0.61866</cdr:y>
+      <cdr:y>0.6237</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.43129</cdr:x>
+      <cdr:x>0.43095</cdr:x>
       <cdr:y>0.91407</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
@@ -4233,8 +4336,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="571500" y="3977613"/>
-          <a:ext cx="3861061" cy="1899311"/>
+          <a:off x="571500" y="4010025"/>
+          <a:ext cx="3857625" cy="1866899"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4386,7 +4489,7 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{CD3C573B-0C34-40C3-BE2D-4CC62EED4169}" name="Kit A"/>
     <tableColumn id="2" xr3:uid="{233C09F4-EFE5-4067-8D0A-727EFB3A34C6}" name="Kit B"/>
-    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="20">
+    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="35">
       <calculatedColumnFormula>6*A2+8*B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{5E73BE8E-91D0-4391-B883-BB1694E2FB56}" name="R1 = Algodão">
@@ -4406,13 +4509,13 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{243F2FF8-6FFB-48E8-A0A8-9E27635C554E}" name="Mesa"/>
     <tableColumn id="2" xr3:uid="{936CC617-A79F-4905-94F7-13BFF79EEC6B}" name="Armario"/>
-    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="19">
+    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="34">
       <calculatedColumnFormula>4*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="18">
+    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="33">
       <calculatedColumnFormula>2*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="17">
+    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="32">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4421,19 +4524,22 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D4E9F9F4-33C9-4351-8E5E-FE895863D27C}" name="Tabela134" displayName="Tabela134" ref="A1:E7" totalsRowShown="0">
-  <autoFilter ref="A1:E7" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D4E9F9F4-33C9-4351-8E5E-FE895863D27C}" name="Tabela134" displayName="Tabela134" ref="A1:F8" totalsRowShown="0">
+  <autoFilter ref="A1:F8" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7142BF79-17B1-4B0B-A34F-7AAA22690851}" name="B1"/>
     <tableColumn id="2" xr3:uid="{253F461F-5BA1-4522-9AFC-63887ECB9A1D}" name="B2"/>
-    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="16">
+    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="31">
       <calculatedColumnFormula>8*A2+5*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="11">
+    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="30">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="29">
       <calculatedColumnFormula>3*A2+4*B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{7CE4A843-9C9A-4225-A098-090E08502E57}" name="R3=MKT" dataDxfId="11">
+      <calculatedColumnFormula>A2+B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4864,12 +4970,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="lessThanOrEqual">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="lessThanOrEqual">
       <formula>84</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5010,20 +5116,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="lessThanOrEqual">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThanOrEqual">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5037,16 +5143,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6E2673-FA2C-4936-AC92-6D9FE69529DB}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.140625" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -5062,12 +5169,15 @@
       <c r="E1" t="s">
         <v>10</v>
       </c>
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
         <v>0</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>1000</v>
       </c>
       <c r="C2" s="1">
@@ -5082,12 +5192,16 @@
         <f t="shared" ref="E2:E6" si="2">3*A2+4*B2</f>
         <v>4000</v>
       </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F9" si="3">A2+B2</f>
+        <v>1000</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
         <v>500</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>0</v>
       </c>
       <c r="C3" s="1">
@@ -5102,12 +5216,16 @@
         <f t="shared" si="2"/>
         <v>1500</v>
       </c>
+      <c r="F3">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
         <v>0</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="16">
         <v>600</v>
       </c>
       <c r="C4" s="1">
@@ -5122,12 +5240,16 @@
         <f t="shared" si="2"/>
         <v>2400</v>
       </c>
+      <c r="F4">
+        <f t="shared" si="3"/>
+        <v>600</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
         <v>800</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="18">
         <v>0</v>
       </c>
       <c r="C5" s="1">
@@ -5142,12 +5264,16 @@
         <f t="shared" si="2"/>
         <v>2400</v>
       </c>
+      <c r="F5">
+        <f t="shared" si="3"/>
+        <v>800</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>0</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="19">
         <v>700</v>
       </c>
       <c r="C6" s="1">
@@ -5155,19 +5281,23 @@
         <v>3500</v>
       </c>
       <c r="D6">
-        <f t="shared" ref="D6:D7" si="3">2*A6+1*B6</f>
+        <f t="shared" ref="D6:D7" si="4">2*A6+1*B6</f>
         <v>700</v>
       </c>
       <c r="E6">
         <f t="shared" si="2"/>
         <v>2800</v>
       </c>
+      <c r="F6">
+        <f t="shared" si="3"/>
+        <v>700</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>700</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="19">
         <v>0</v>
       </c>
       <c r="C7" s="1">
@@ -5175,100 +5305,147 @@
         <v>5600</v>
       </c>
       <c r="D7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1400</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="8">
         <f>3*A7+4*B7</f>
         <v>2100</v>
       </c>
+      <c r="F7">
+        <f t="shared" si="3"/>
+        <v>700</v>
+      </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="6"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>320</v>
+      </c>
+      <c r="B8">
+        <v>360</v>
+      </c>
+      <c r="C8" s="1">
+        <f>8*A8+5*B8</f>
+        <v>4360</v>
+      </c>
+      <c r="D8" s="8">
+        <f>2*A8+1*B8</f>
+        <v>1000</v>
+      </c>
+      <c r="E8" s="8">
+        <f>3*A8+4*B8</f>
+        <v>2400</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="3"/>
+        <v>680</v>
+      </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
       <c r="D15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="10"/>
+      <c r="B17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="C19" s="3"/>
       <c r="D19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="C20" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A15:C15"/>
   </mergeCells>
-  <conditionalFormatting sqref="E8:E10 E14:E1048576">
+  <conditionalFormatting sqref="E8 E14:E1048576 E10">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E8">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThanOrEqual">
+      <formula>2400</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D8">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="lessThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F8">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
+      <formula>700</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>8</formula>
     </cfRule>

--- a/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
+++ b/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8757B584-31A5-4D35-8CC3-E150B2E3D745}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261DF0EB-B06B-4E88-B748-283046F253EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
   </bookViews>

--- a/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
+++ b/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261DF0EB-B06B-4E88-B748-283046F253EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F88678-AF40-4CE7-9534-6C64D6610A3F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="3" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
   </bookViews>
   <sheets>
     <sheet name="MEIAS" sheetId="1" r:id="rId1"/>
     <sheet name="MARCENARIA" sheetId="3" r:id="rId2"/>
     <sheet name="FABRICA DE BRINQUEDOS" sheetId="4" r:id="rId3"/>
+    <sheet name="FABRICA DE FANTASIAS" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>Função Objetivo</t>
   </si>
@@ -102,6 +103,51 @@
   </si>
   <si>
     <t>R3=MKT</t>
+  </si>
+  <si>
+    <t>BRIM</t>
+  </si>
+  <si>
+    <t>SEDA</t>
+  </si>
+  <si>
+    <t>CETIM</t>
+  </si>
+  <si>
+    <t>M1= QTD. DE FANTASIAS A SER PRODUZIDA</t>
+  </si>
+  <si>
+    <t>M2= QTD. DE FANTASIAS A SER PRODUZIDA</t>
+  </si>
+  <si>
+    <t>300*M1+500*M2</t>
+  </si>
+  <si>
+    <t>4m1+2m2&lt;=32</t>
+  </si>
+  <si>
+    <t>2m1+4m2&lt;=22</t>
+  </si>
+  <si>
+    <t>2m1+6m2&lt;=30</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>R1 = BRIM</t>
+  </si>
+  <si>
+    <t>R2 = SEDA</t>
+  </si>
+  <si>
+    <t>R3=CETIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Função Objetivo = Max(Receita) </t>
   </si>
 </sst>
 </file>
@@ -324,7 +370,7 @@
     <cellStyle name="Neutro" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="38">
     <dxf>
       <fill>
         <patternFill>
@@ -357,6 +403,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -366,6 +419,27 @@
         <patternFill patternType="solid">
           <fgColor auto="1"/>
           <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -409,16 +483,24 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -437,6 +519,16 @@
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <fill>
@@ -477,56 +569,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2125,6 +2167,542 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>FANTASIAS</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'FABRICA DE FANTASIAS'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>M2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'FABRICA DE FANTASIAS'!$A$2:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'FABRICA DE FANTASIAS'!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FB5E-4360-B549-C6686668E7DC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="r"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="812372704"/>
+        <c:axId val="819850496"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="812372704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>M1</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="819850496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="819850496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>M2</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="812372704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2245,6 +2823,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3278,6 +3896,522 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4483,13 +5617,277 @@
 </c:userShapes>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>514351</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7DEACCF-70A3-4C6C-B602-68E674321FFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.05468</cdr:x>
+      <cdr:y>0.15556</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.52117</cdr:x>
+      <cdr:y>0.90806</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="5" name="Conector reto 4">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F198E37C-AED7-41C3-93D9-60888376F771}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="561975" y="1000125"/>
+          <a:ext cx="4794369" cy="4838140"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.05669</cdr:x>
+      <cdr:y>0.72296</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.22806</cdr:x>
+      <cdr:y>0.91053</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="8" name="Retângulo 7">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{550D4823-7B28-4307-8AA8-6EA5F26D80B4}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="582670" y="4648200"/>
+          <a:ext cx="1761173" cy="1205907"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="wdDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="bg1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="tx2">
+              <a:alpha val="16000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.05746</cdr:x>
+      <cdr:y>0.67556</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.92322</cdr:x>
+      <cdr:y>0.90806</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="9" name="Conector reto 8">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FF22B94-90AB-4F3C-BCDC-110E3292018C}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="590550" y="4343400"/>
+          <a:ext cx="8897783" cy="1494865"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.05375</cdr:x>
+      <cdr:y>0.65185</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.69583</cdr:x>
+      <cdr:y>0.9098</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="17" name="Conector reto 16">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0DA861A-7626-43F8-A5F5-814BBB4A6B0A}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="552450" y="4191000"/>
+          <a:ext cx="6598938" cy="1658471"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B92EF86-C117-4AAB-83FC-A9F29285C342}" name="Tabela1" displayName="Tabela1" ref="A1:E6" totalsRowShown="0">
   <autoFilter ref="A1:E6" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{CD3C573B-0C34-40C3-BE2D-4CC62EED4169}" name="Kit A"/>
     <tableColumn id="2" xr3:uid="{233C09F4-EFE5-4067-8D0A-727EFB3A34C6}" name="Kit B"/>
-    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="35">
+    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="37">
       <calculatedColumnFormula>6*A2+8*B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{5E73BE8E-91D0-4391-B883-BB1694E2FB56}" name="R1 = Algodão">
@@ -4509,13 +5907,13 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{243F2FF8-6FFB-48E8-A0A8-9E27635C554E}" name="Mesa"/>
     <tableColumn id="2" xr3:uid="{936CC617-A79F-4905-94F7-13BFF79EEC6B}" name="Armario"/>
-    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="34">
+    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="36">
       <calculatedColumnFormula>4*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="33">
+    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="35">
       <calculatedColumnFormula>2*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="32">
+    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="34">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4529,17 +5927,40 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7142BF79-17B1-4B0B-A34F-7AAA22690851}" name="B1"/>
     <tableColumn id="2" xr3:uid="{253F461F-5BA1-4522-9AFC-63887ECB9A1D}" name="B2"/>
-    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="31">
+    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="33">
       <calculatedColumnFormula>8*A2+5*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="30">
+    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="32">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="29">
+    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="31">
       <calculatedColumnFormula>3*A2+4*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7CE4A843-9C9A-4225-A098-090E08502E57}" name="R3=MKT" dataDxfId="11">
+    <tableColumn id="6" xr3:uid="{7CE4A843-9C9A-4225-A098-090E08502E57}" name="R3=MKT" dataDxfId="24">
       <calculatedColumnFormula>A2+B2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0F1801BC-FE1F-4697-A185-FFCA42E25099}" name="Tabela1346" displayName="Tabela1346" ref="A1:F8" totalsRowShown="0">
+  <autoFilter ref="A1:F8" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{FD3EED3F-96B3-4FDE-AFC1-CF9AB480BDFD}" name="M1"/>
+    <tableColumn id="2" xr3:uid="{D6586624-7B2C-4F00-9453-AC439F616919}" name="M2"/>
+    <tableColumn id="3" xr3:uid="{429BC477-66F4-478A-926F-E64E52559C3F}" name="Função Objetivo" dataDxfId="18">
+      <calculatedColumnFormula>300*A2+500*B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{1CF4E565-70C8-4C29-89F5-04FD354176A2}" name="R1 = BRIM" dataDxfId="17">
+      <calculatedColumnFormula>4*A2+2*B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{89C0C742-1380-43DB-B89E-4A4E165CA1CF}" name="R2 = SEDA" dataDxfId="16">
+      <calculatedColumnFormula>2*A2+4*B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{584571AF-6EE5-49D0-8E7E-3814C85D9368}" name="R3=CETIM" dataDxfId="15">
+      <calculatedColumnFormula>2*A2+6*B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4970,12 +6391,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="lessThanOrEqual">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="lessThanOrEqual">
       <formula>84</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5116,20 +6537,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="lessThanOrEqual">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="lessThanOrEqual">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E1048576">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5426,27 +6847,341 @@
     <mergeCell ref="A15:C15"/>
   </mergeCells>
   <conditionalFormatting sqref="E8 E14:E1048576 E10">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E8">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="lessThanOrEqual">
       <formula>2400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="lessThanOrEqual">
       <formula>700</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8537F293-47D4-402B-933E-7B3A96B7FA55}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1">
+        <f t="shared" ref="C2:C8" si="0">300*A2+500*B2</f>
+        <v>8000</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:D8" si="1">4*A2+2*B2</f>
+        <v>32</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ref="E2:E8" si="2">2*A2+4*B2</f>
+        <v>64</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F8" si="3">2*A2+6*B2</f>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>8</v>
+      </c>
+      <c r="B3" s="13">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>0</v>
+      </c>
+      <c r="B4" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" si="0"/>
+        <v>2750</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>11</v>
+      </c>
+      <c r="B5" s="18">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="0"/>
+        <v>3300</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>0</v>
+      </c>
+      <c r="B6" s="19">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>15</v>
+      </c>
+      <c r="B7" s="19">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>2900</v>
+      </c>
+      <c r="D8" s="8">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="E8" s="8">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B18:C18"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E8 E14:E1048576 E10">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E8">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThanOrEqual">
+      <formula>22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D8">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThanOrEqual">
+      <formula>32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F8">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThanOrEqual">
+      <formula>30</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
+++ b/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F88678-AF40-4CE7-9534-6C64D6610A3F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EB57ED-6A53-49FC-94C9-873C42898F06}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="3" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="4" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
   </bookViews>
   <sheets>
     <sheet name="MEIAS" sheetId="1" r:id="rId1"/>
     <sheet name="MARCENARIA" sheetId="3" r:id="rId2"/>
     <sheet name="FABRICA DE BRINQUEDOS" sheetId="4" r:id="rId3"/>
     <sheet name="FABRICA DE FANTASIAS" sheetId="5" r:id="rId4"/>
+    <sheet name="BARCO" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
   <si>
     <t>Função Objetivo</t>
   </si>
@@ -149,6 +150,54 @@
   <si>
     <t xml:space="preserve">Função Objetivo = Max(Receita) </t>
   </si>
+  <si>
+    <t>C= QTD DE CARNE A SER TRANSPORTADA</t>
+  </si>
+  <si>
+    <t>G= QTD. DE GRÃOS A SER TRANSPORTADA</t>
+  </si>
+  <si>
+    <t>CARNE DISPONIVEL</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Função Objetivo = Max(LUCRO) </t>
+  </si>
+  <si>
+    <t>0,35*C+0,12*G</t>
+  </si>
+  <si>
+    <t>R1 = CARNE</t>
+  </si>
+  <si>
+    <t>R2 = GRÃO</t>
+  </si>
+  <si>
+    <t>R3=ESPAÇO NAVIO</t>
+  </si>
+  <si>
+    <t>R4= CPC EM KG</t>
+  </si>
+  <si>
+    <t>GRAOS DISPONIVEL</t>
+  </si>
+  <si>
+    <t>ESPAÇO NAVIO</t>
+  </si>
+  <si>
+    <t>0,2*C+0,4*G&lt;=70000</t>
+  </si>
+  <si>
+    <t>CPC KG</t>
+  </si>
+  <si>
+    <t>C+G=160000</t>
+  </si>
 </sst>
 </file>
 
@@ -241,7 +290,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -323,6 +372,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -331,7 +417,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -362,6 +448,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bom" xfId="1" builtinId="26"/>
@@ -370,11 +462,103 @@
     <cellStyle name="Neutro" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="62">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF9999"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -416,49 +600,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
@@ -478,57 +619,6 @@
           <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <fill>
@@ -571,6 +661,134 @@
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2344,10 +2562,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'FABRICA DE FANTASIAS'!$A$2:$A$8</c:f>
+              <c:f>'FABRICA DE FANTASIAS'!$A$2:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2369,15 +2587,18 @@
                 <c:pt idx="6">
                   <c:v>3</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FABRICA DE FANTASIAS'!$B$2:$B$8</c:f>
+              <c:f>'FABRICA DE FANTASIAS'!$B$2:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>16</c:v>
                 </c:pt>
@@ -2398,6 +2619,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2703,6 +2927,536 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>BARCO</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>BARCO!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>G</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>BARCO!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0" formatCode="#,##0">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>160</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>BARCO!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A698-4B57-8D91-5C42A2A34610}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="r"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="812372704"/>
+        <c:axId val="819850496"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="812372704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>C</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="819850496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="819850496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>G</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="812372704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2863,6 +3617,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -4412,6 +5206,522 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4966,6 +6276,272 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.0381</cdr:x>
+      <cdr:y>0.47097</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.89419</cdr:x>
+      <cdr:y>0.47419</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="5" name="Conector reto 4">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F198E37C-AED7-41C3-93D9-60888376F771}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="621366" y="3272118"/>
+          <a:ext cx="13962530" cy="22411"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.5332</cdr:x>
+      <cdr:y>0.17305</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.93946</cdr:x>
+      <cdr:y>0.26615</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="8" name="Retângulo 7">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{550D4823-7B28-4307-8AA8-6EA5F26D80B4}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5767956" y="1116502"/>
+          <a:ext cx="4394757" cy="600662"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="wdDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="bg1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="tx2">
+              <a:alpha val="16000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.0381</cdr:x>
+      <cdr:y>0.20806</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.44828</cdr:x>
+      <cdr:y>0.91613</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="9" name="Conector reto 8">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FF22B94-90AB-4F3C-BCDC-110E3292018C}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="621366" y="1445559"/>
+          <a:ext cx="6689912" cy="4919382"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.25521</cdr:x>
+      <cdr:y>0.09355</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.25659</cdr:x>
+      <cdr:y>0.91613</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="17" name="Conector reto 16">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0DA861A-7626-43F8-A5F5-814BBB4A6B0A}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="4162425" y="649941"/>
+          <a:ext cx="22412" cy="5715000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.03672</cdr:x>
+      <cdr:y>0.1371</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.93542</cdr:x>
+      <cdr:y>0.91613</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="26" name="Conector reto 25">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD5B0180-21AA-4728-8B91-CB2CE3829D3E}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="598955" y="952500"/>
+          <a:ext cx="14657294" cy="5412441"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5715,10 +7291,10 @@
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
       <cdr:x>0.05669</cdr:x>
-      <cdr:y>0.72296</cdr:y>
+      <cdr:y>0.81743</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.22806</cdr:x>
+      <cdr:x>0.46295</cdr:x>
       <cdr:y>0.91053</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
@@ -5734,8 +7310,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="582670" y="4648200"/>
-          <a:ext cx="1761173" cy="1205907"/>
+          <a:off x="578350" y="5255559"/>
+          <a:ext cx="4144369" cy="598548"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5881,13 +7457,56 @@
 </c:userShapes>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>230281</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>201706</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>67234</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41563817-3934-4A79-82F5-6890FCCFFB8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B92EF86-C117-4AAB-83FC-A9F29285C342}" name="Tabela1" displayName="Tabela1" ref="A1:E6" totalsRowShown="0">
   <autoFilter ref="A1:E6" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{CD3C573B-0C34-40C3-BE2D-4CC62EED4169}" name="Kit A"/>
     <tableColumn id="2" xr3:uid="{233C09F4-EFE5-4067-8D0A-727EFB3A34C6}" name="Kit B"/>
-    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="37">
+    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="61">
       <calculatedColumnFormula>6*A2+8*B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{5E73BE8E-91D0-4391-B883-BB1694E2FB56}" name="R1 = Algodão">
@@ -5907,13 +7526,13 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{243F2FF8-6FFB-48E8-A0A8-9E27635C554E}" name="Mesa"/>
     <tableColumn id="2" xr3:uid="{936CC617-A79F-4905-94F7-13BFF79EEC6B}" name="Armario"/>
-    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="36">
+    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="60">
       <calculatedColumnFormula>4*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="35">
+    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="59">
       <calculatedColumnFormula>2*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="34">
+    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="58">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5927,16 +7546,16 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7142BF79-17B1-4B0B-A34F-7AAA22690851}" name="B1"/>
     <tableColumn id="2" xr3:uid="{253F461F-5BA1-4522-9AFC-63887ECB9A1D}" name="B2"/>
-    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="33">
+    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="57">
       <calculatedColumnFormula>8*A2+5*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="32">
+    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="56">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="31">
+    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="55">
       <calculatedColumnFormula>3*A2+4*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7CE4A843-9C9A-4225-A098-090E08502E57}" name="R3=MKT" dataDxfId="24">
+    <tableColumn id="6" xr3:uid="{7CE4A843-9C9A-4225-A098-090E08502E57}" name="R3=MKT" dataDxfId="54">
       <calculatedColumnFormula>A2+B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5945,22 +7564,74 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0F1801BC-FE1F-4697-A185-FFCA42E25099}" name="Tabela1346" displayName="Tabela1346" ref="A1:F8" totalsRowShown="0">
-  <autoFilter ref="A1:F8" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0F1801BC-FE1F-4697-A185-FFCA42E25099}" name="Tabela1346" displayName="Tabela1346" ref="A1:F9" totalsRowShown="0">
+  <autoFilter ref="A1:F9" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{FD3EED3F-96B3-4FDE-AFC1-CF9AB480BDFD}" name="M1"/>
     <tableColumn id="2" xr3:uid="{D6586624-7B2C-4F00-9453-AC439F616919}" name="M2"/>
-    <tableColumn id="3" xr3:uid="{429BC477-66F4-478A-926F-E64E52559C3F}" name="Função Objetivo" dataDxfId="18">
+    <tableColumn id="3" xr3:uid="{429BC477-66F4-478A-926F-E64E52559C3F}" name="Função Objetivo" dataDxfId="53">
       <calculatedColumnFormula>300*A2+500*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1CF4E565-70C8-4C29-89F5-04FD354176A2}" name="R1 = BRIM" dataDxfId="17">
+    <tableColumn id="4" xr3:uid="{1CF4E565-70C8-4C29-89F5-04FD354176A2}" name="R1 = BRIM" dataDxfId="52">
       <calculatedColumnFormula>4*A2+2*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{89C0C742-1380-43DB-B89E-4A4E165CA1CF}" name="R2 = SEDA" dataDxfId="16">
+    <tableColumn id="5" xr3:uid="{89C0C742-1380-43DB-B89E-4A4E165CA1CF}" name="R2 = SEDA" dataDxfId="51">
       <calculatedColumnFormula>2*A2+4*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{584571AF-6EE5-49D0-8E7E-3814C85D9368}" name="R3=CETIM" dataDxfId="15">
+    <tableColumn id="6" xr3:uid="{584571AF-6EE5-49D0-8E7E-3814C85D9368}" name="R3=CETIM" dataDxfId="50">
       <calculatedColumnFormula>2*A2+6*B2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1FF2970B-E0AC-41B6-9EB1-FD026D58DD9F}" name="Tabela13467" displayName="Tabela13467" ref="A1:G9" totalsRowShown="0">
+  <autoFilter ref="A1:G9" xr:uid="{CBAE266A-04DC-45EF-8B1A-B772638344D1}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{BEDCB459-658A-48BA-BAB3-B60F1BE82A96}" name="C"/>
+    <tableColumn id="2" xr3:uid="{B12FF819-3198-4046-880B-F57B166EE056}" name="G"/>
+    <tableColumn id="3" xr3:uid="{8D0F86AF-1313-4F43-B1FA-0B0C139C49B3}" name="Função Objetivo" dataDxfId="49">
+      <calculatedColumnFormula>0.35*A2+0.12*B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{FB68FF3A-4860-40D1-8C87-437DC263A7E6}" name="R1 = CARNE" dataDxfId="48">
+      <calculatedColumnFormula>Tabela13467[[#This Row],[C]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{51987C58-626D-4410-BDF7-28722C354186}" name="R2 = GRÃO" dataDxfId="47">
+      <calculatedColumnFormula>Tabela13467[[#This Row],[G]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{272BC6B7-E1DF-4A0B-8B9D-EF6ACAD22ADD}" name="R3=ESPAÇO NAVIO" dataDxfId="43">
+      <calculatedColumnFormula>0.2*A2+0.4*B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{3B766D69-B18A-4888-A22A-5028240B0F29}" name="R4= CPC EM KG" dataDxfId="42">
+      <calculatedColumnFormula>A2+B2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{63E25B8C-242D-4EF5-8F23-ECF39180D0EA}" name="Tabela134679" displayName="Tabela134679" ref="A28:G36" totalsRowShown="0">
+  <autoFilter ref="A28:G36" xr:uid="{C84A06B6-2522-4BC3-AE72-C77D9276D38E}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{A3831E57-CE77-4DC8-922B-34B66CEDBBA4}" name="C"/>
+    <tableColumn id="2" xr3:uid="{3ED68ABD-0E71-41BB-A50F-7D5BA3D80E0C}" name="G"/>
+    <tableColumn id="3" xr3:uid="{19B4EDC3-B38E-4E10-82F1-2FA6714E8139}" name="Função Objetivo" dataDxfId="8">
+      <calculatedColumnFormula>0.35*A29+0.12*B29</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{21BDE719-3563-4B51-858E-43F7CAE64A94}" name="R1 = CARNE" dataDxfId="7">
+      <calculatedColumnFormula>Tabela134679[[#This Row],[C]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{6F1C6C99-053C-4C07-84E6-085F8607091C}" name="R2 = GRÃO" dataDxfId="6">
+      <calculatedColumnFormula>Tabela134679[[#This Row],[G]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{66ED4DE3-9CD8-4341-82C5-4EB9293498B0}" name="R3=ESPAÇO NAVIO" dataDxfId="5">
+      <calculatedColumnFormula>0.2*A29+0.4*B29</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{46646406-2261-4189-8B34-B5D0553D4D09}" name="R4= CPC EM KG" dataDxfId="4">
+      <calculatedColumnFormula>A29+B29</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6847,27 +8518,27 @@
     <mergeCell ref="A15:C15"/>
   </mergeCells>
   <conditionalFormatting sqref="E8 E14:E1048576 E10">
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E8">
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
       <formula>2400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8">
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="lessThanOrEqual">
       <formula>700</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7055,7 +8726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -7077,6 +8748,30 @@
       <c r="F8">
         <f t="shared" si="3"/>
         <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
+        <v>7</v>
+      </c>
+      <c r="B9" s="21">
+        <v>2</v>
+      </c>
+      <c r="C9" s="22">
+        <f>300*A9+500*B9</f>
+        <v>3100</v>
+      </c>
+      <c r="D9" s="23">
+        <f>4*A9+2*B9</f>
+        <v>32</v>
+      </c>
+      <c r="E9" s="23">
+        <f>2*A9+4*B9</f>
+        <v>22</v>
+      </c>
+      <c r="F9" s="24">
+        <f>2*A9+6*B9</f>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -7160,29 +8855,19 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B18:C18"/>
   </mergeCells>
-  <conditionalFormatting sqref="E8 E14:E1048576 E10">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="E2:E9">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThanOrEqual">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="F2:F9">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="lessThanOrEqual">
       <formula>30</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
-      <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -7191,4 +8876,639 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34A350A-92B4-4B3D-B03D-0A96FDFF2C25}">
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>85</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <f t="shared" ref="C2:C9" si="0">0.35*A2+0.12*B2</f>
+        <v>29.749999999999996</v>
+      </c>
+      <c r="D2">
+        <f>Tabela13467[[#This Row],[C]]</f>
+        <v>85</v>
+      </c>
+      <c r="E2">
+        <f>Tabela13467[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F9" si="1">0.2*A2+0.4*B2</f>
+        <v>17</v>
+      </c>
+      <c r="G2" s="8">
+        <f t="shared" ref="G2:G9" si="2">A2+B2</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14">
+        <v>0</v>
+      </c>
+      <c r="B3" s="14">
+        <v>100</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <f>Tabela13467[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>Tabela13467[[#This Row],[G]]</f>
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="G3" s="8">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
+        <v>0</v>
+      </c>
+      <c r="B4" s="19">
+        <v>175</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <f>Tabela13467[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>Tabela13467[[#This Row],[G]]</f>
+        <v>175</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="G4" s="8">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
+        <v>350</v>
+      </c>
+      <c r="B5" s="19">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="0"/>
+        <v>122.49999999999999</v>
+      </c>
+      <c r="D5">
+        <f>Tabela13467[[#This Row],[C]]</f>
+        <v>350</v>
+      </c>
+      <c r="E5">
+        <f>Tabela13467[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>160</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>19.2</v>
+      </c>
+      <c r="D6">
+        <f>Tabela13467[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>Tabela13467[[#This Row],[G]]</f>
+        <v>160</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="G6" s="8">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>160</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="D7">
+        <f>Tabela13467[[#This Row],[C]]</f>
+        <v>160</v>
+      </c>
+      <c r="E7" s="8">
+        <f>Tabela13467[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f>Tabela13467[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="8">
+        <f>Tabela13467[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f>Tabela13467[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="8">
+        <f>Tabela13467[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3">
+        <v>85000</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="3">
+        <v>100000</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>85</v>
+      </c>
+      <c r="B29" s="11">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" ref="C29:C36" si="3">0.35*A29+0.12*B29</f>
+        <v>29.749999999999996</v>
+      </c>
+      <c r="D29">
+        <f>Tabela134679[[#This Row],[C]]</f>
+        <v>85</v>
+      </c>
+      <c r="E29">
+        <f>Tabela134679[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <f t="shared" ref="F29:F36" si="4">0.2*A29+0.4*B29</f>
+        <v>17</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" ref="G29:G36" si="5">A29+B29</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <v>0</v>
+      </c>
+      <c r="B30" s="14">
+        <v>100</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="D30">
+        <f>Tabela134679[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <f>Tabela134679[[#This Row],[G]]</f>
+        <v>100</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="G30" s="8">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>0</v>
+      </c>
+      <c r="B31" s="19">
+        <v>175</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="D31">
+        <f>Tabela134679[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <f>Tabela134679[[#This Row],[G]]</f>
+        <v>175</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="G31" s="8">
+        <f t="shared" si="5"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>350</v>
+      </c>
+      <c r="B32" s="19">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="3"/>
+        <v>122.49999999999999</v>
+      </c>
+      <c r="D32">
+        <f>Tabela134679[[#This Row],[C]]</f>
+        <v>350</v>
+      </c>
+      <c r="E32">
+        <f>Tabela134679[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="G32" s="8">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33">
+        <v>160</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="3"/>
+        <v>19.2</v>
+      </c>
+      <c r="D33">
+        <f>Tabela134679[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <f>Tabela134679[[#This Row],[G]]</f>
+        <v>160</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+      <c r="G33" s="8">
+        <f t="shared" si="5"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>160</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="D34">
+        <f>Tabela134679[[#This Row],[C]]</f>
+        <v>160</v>
+      </c>
+      <c r="E34" s="8">
+        <f>Tabela134679[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="G34" s="8">
+        <f t="shared" si="5"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f>Tabela134679[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
+        <f>Tabela134679[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="20"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f>Tabela134679[[#This Row],[C]]</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="23">
+        <f>Tabela134679[[#This Row],[G]]</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B18:C18"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="cellIs" dxfId="16" priority="14" operator="greaterThanOrEqual">
+      <formula>85000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E8">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="greaterThanOrEqual">
+      <formula>100000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F8">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="greaterThanOrEqual">
+      <formula>70000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G9">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="greaterThanOrEqual">
+      <formula>85000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D36">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="greaterThanOrEqual">
+      <formula>85000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:E36">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
+      <formula>100000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F36">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="greaterThanOrEqual">
+      <formula>70000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29:G36">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThanOrEqual">
+      <formula>85000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
+      <formula>100000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThanOrEqual">
+      <formula>70000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
+++ b/Arquivos/CONSTRUÇÃO DE GRAFICO - VENDEDOR DE MEIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EB57ED-6A53-49FC-94C9-873C42898F06}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C11500-6BE8-4093-9B2E-934CCD2070CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="4" xr2:uid="{8AC3BFE0-796C-44EF-8B5F-5E49284BBC29}"/>
   </bookViews>
@@ -462,49 +462,13 @@
     <cellStyle name="Neutro" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="68">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
       <fill>
@@ -561,6 +525,182 @@
           <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
       <fill>
@@ -663,108 +803,10 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3126,6 +3168,12 @@
                 <c:pt idx="5">
                   <c:v>160</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3152,6 +3200,12 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6332,12 +6386,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.5332</cdr:x>
-      <cdr:y>0.17305</cdr:y>
+      <cdr:x>0.03576</cdr:x>
+      <cdr:y>0.47467</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.93946</cdr:x>
-      <cdr:y>0.26615</cdr:y>
+      <cdr:x>0.19338</cdr:x>
+      <cdr:y>0.92419</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6352,8 +6406,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5767956" y="1116502"/>
-          <a:ext cx="4394757" cy="600662"/>
+          <a:off x="583239" y="3297811"/>
+          <a:ext cx="2570657" cy="3123159"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6540,6 +6594,166 @@
         </a:fontRef>
       </cdr:style>
     </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.03535</cdr:x>
+      <cdr:y>0.58387</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.2559</cdr:x>
+      <cdr:y>0.92136</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="28" name="Retângulo 27">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA174F3C-0E47-42CB-8140-99DD63837FEA}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="576544" y="4056529"/>
+          <a:ext cx="3597088" cy="2344724"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="wdDnDiag">
+          <a:fgClr>
+            <a:srgbClr val="7030A0"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="bg1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:schemeClr val="tx2">
+              <a:alpha val="86000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
   </cdr:relSizeAnchor>
 </c:userShapes>
 </file>
@@ -7506,7 +7720,7 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{CD3C573B-0C34-40C3-BE2D-4CC62EED4169}" name="Kit A"/>
     <tableColumn id="2" xr3:uid="{233C09F4-EFE5-4067-8D0A-727EFB3A34C6}" name="Kit B"/>
-    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="61">
+    <tableColumn id="3" xr3:uid="{6E957160-AEF8-4502-A6F9-A254FB709B69}" name="Função Objetivo" dataDxfId="67">
       <calculatedColumnFormula>6*A2+8*B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{5E73BE8E-91D0-4391-B883-BB1694E2FB56}" name="R1 = Algodão">
@@ -7526,13 +7740,13 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{243F2FF8-6FFB-48E8-A0A8-9E27635C554E}" name="Mesa"/>
     <tableColumn id="2" xr3:uid="{936CC617-A79F-4905-94F7-13BFF79EEC6B}" name="Armario"/>
-    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="60">
+    <tableColumn id="3" xr3:uid="{D6BAF88C-0AE3-4255-B2FA-BA17ABA26915}" name="Função Objetivo" dataDxfId="66">
       <calculatedColumnFormula>4*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="59">
+    <tableColumn id="4" xr3:uid="{963FD4E7-90E3-4ECF-90B5-A6A166678D50}" name="R1 = Algodão" dataDxfId="65">
       <calculatedColumnFormula>2*A2+3*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="58">
+    <tableColumn id="5" xr3:uid="{12F9FD07-8BE4-4AB5-8264-89A97F8C4BAE}" name="R2 = Lã" dataDxfId="64">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7546,16 +7760,16 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7142BF79-17B1-4B0B-A34F-7AAA22690851}" name="B1"/>
     <tableColumn id="2" xr3:uid="{253F461F-5BA1-4522-9AFC-63887ECB9A1D}" name="B2"/>
-    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="57">
+    <tableColumn id="3" xr3:uid="{84FA9468-B4BC-439B-B885-B2CD2410F99D}" name="Função Objetivo" dataDxfId="63">
       <calculatedColumnFormula>8*A2+5*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="56">
+    <tableColumn id="4" xr3:uid="{5B8EF21A-EE8A-4503-A5BB-136726CBDF0B}" name="R1 = Plastico" dataDxfId="62">
       <calculatedColumnFormula>2*A2+1*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="55">
+    <tableColumn id="5" xr3:uid="{030ED1E5-1D2C-422B-9F13-1D61EBCD9D19}" name="R2 = M.O." dataDxfId="61">
       <calculatedColumnFormula>3*A2+4*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7CE4A843-9C9A-4225-A098-090E08502E57}" name="R3=MKT" dataDxfId="54">
+    <tableColumn id="6" xr3:uid="{7CE4A843-9C9A-4225-A098-090E08502E57}" name="R3=MKT" dataDxfId="60">
       <calculatedColumnFormula>A2+B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7569,16 +7783,16 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{FD3EED3F-96B3-4FDE-AFC1-CF9AB480BDFD}" name="M1"/>
     <tableColumn id="2" xr3:uid="{D6586624-7B2C-4F00-9453-AC439F616919}" name="M2"/>
-    <tableColumn id="3" xr3:uid="{429BC477-66F4-478A-926F-E64E52559C3F}" name="Função Objetivo" dataDxfId="53">
+    <tableColumn id="3" xr3:uid="{429BC477-66F4-478A-926F-E64E52559C3F}" name="Função Objetivo" dataDxfId="59">
       <calculatedColumnFormula>300*A2+500*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1CF4E565-70C8-4C29-89F5-04FD354176A2}" name="R1 = BRIM" dataDxfId="52">
+    <tableColumn id="4" xr3:uid="{1CF4E565-70C8-4C29-89F5-04FD354176A2}" name="R1 = BRIM" dataDxfId="58">
       <calculatedColumnFormula>4*A2+2*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{89C0C742-1380-43DB-B89E-4A4E165CA1CF}" name="R2 = SEDA" dataDxfId="51">
+    <tableColumn id="5" xr3:uid="{89C0C742-1380-43DB-B89E-4A4E165CA1CF}" name="R2 = SEDA" dataDxfId="57">
       <calculatedColumnFormula>2*A2+4*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{584571AF-6EE5-49D0-8E7E-3814C85D9368}" name="R3=CETIM" dataDxfId="50">
+    <tableColumn id="6" xr3:uid="{584571AF-6EE5-49D0-8E7E-3814C85D9368}" name="R3=CETIM" dataDxfId="56">
       <calculatedColumnFormula>2*A2+6*B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7592,19 +7806,19 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{BEDCB459-658A-48BA-BAB3-B60F1BE82A96}" name="C"/>
     <tableColumn id="2" xr3:uid="{B12FF819-3198-4046-880B-F57B166EE056}" name="G"/>
-    <tableColumn id="3" xr3:uid="{8D0F86AF-1313-4F43-B1FA-0B0C139C49B3}" name="Função Objetivo" dataDxfId="49">
+    <tableColumn id="3" xr3:uid="{8D0F86AF-1313-4F43-B1FA-0B0C139C49B3}" name="Função Objetivo" dataDxfId="55">
       <calculatedColumnFormula>0.35*A2+0.12*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FB68FF3A-4860-40D1-8C87-437DC263A7E6}" name="R1 = CARNE" dataDxfId="48">
+    <tableColumn id="4" xr3:uid="{FB68FF3A-4860-40D1-8C87-437DC263A7E6}" name="R1 = CARNE" dataDxfId="54">
       <calculatedColumnFormula>Tabela13467[[#This Row],[C]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{51987C58-626D-4410-BDF7-28722C354186}" name="R2 = GRÃO" dataDxfId="47">
+    <tableColumn id="5" xr3:uid="{51987C58-626D-4410-BDF7-28722C354186}" name="R2 = GRÃO" dataDxfId="53">
       <calculatedColumnFormula>Tabela13467[[#This Row],[G]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{272BC6B7-E1DF-4A0B-8B9D-EF6ACAD22ADD}" name="R3=ESPAÇO NAVIO" dataDxfId="43">
+    <tableColumn id="6" xr3:uid="{272BC6B7-E1DF-4A0B-8B9D-EF6ACAD22ADD}" name="R3=ESPAÇO NAVIO" dataDxfId="52">
       <calculatedColumnFormula>0.2*A2+0.4*B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3B766D69-B18A-4888-A22A-5028240B0F29}" name="R4= CPC EM KG" dataDxfId="42">
+    <tableColumn id="7" xr3:uid="{3B766D69-B18A-4888-A22A-5028240B0F29}" name="R4= CPC EM KG" dataDxfId="51">
       <calculatedColumnFormula>A2+B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7618,19 +7832,19 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A3831E57-CE77-4DC8-922B-34B66CEDBBA4}" name="C"/>
     <tableColumn id="2" xr3:uid="{3ED68ABD-0E71-41BB-A50F-7D5BA3D80E0C}" name="G"/>
-    <tableColumn id="3" xr3:uid="{19B4EDC3-B38E-4E10-82F1-2FA6714E8139}" name="Função Objetivo" dataDxfId="8">
+    <tableColumn id="3" xr3:uid="{19B4EDC3-B38E-4E10-82F1-2FA6714E8139}" name="Função Objetivo" dataDxfId="36">
       <calculatedColumnFormula>0.35*A29+0.12*B29</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{21BDE719-3563-4B51-858E-43F7CAE64A94}" name="R1 = CARNE" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{21BDE719-3563-4B51-858E-43F7CAE64A94}" name="R1 = CARNE" dataDxfId="35">
       <calculatedColumnFormula>Tabela134679[[#This Row],[C]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6F1C6C99-053C-4C07-84E6-085F8607091C}" name="R2 = GRÃO" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{6F1C6C99-053C-4C07-84E6-085F8607091C}" name="R2 = GRÃO" dataDxfId="34">
       <calculatedColumnFormula>Tabela134679[[#This Row],[G]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{66ED4DE3-9CD8-4341-82C5-4EB9293498B0}" name="R3=ESPAÇO NAVIO" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{66ED4DE3-9CD8-4341-82C5-4EB9293498B0}" name="R3=ESPAÇO NAVIO" dataDxfId="33">
       <calculatedColumnFormula>0.2*A29+0.4*B29</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{46646406-2261-4189-8B34-B5D0553D4D09}" name="R4= CPC EM KG" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{46646406-2261-4189-8B34-B5D0553D4D09}" name="R4= CPC EM KG" dataDxfId="32">
       <calculatedColumnFormula>A29+B29</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8062,12 +8276,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="50" priority="2" operator="lessThanOrEqual">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="lessThanOrEqual">
       <formula>84</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8208,20 +8422,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="lessThanOrEqual">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="lessThanOrEqual">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E1048576">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8518,27 +8732,27 @@
     <mergeCell ref="A15:C15"/>
   </mergeCells>
   <conditionalFormatting sqref="E8 E14:E1048576 E10">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="5" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E8">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="43" priority="4" operator="lessThanOrEqual">
       <formula>2400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="lessThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="41" priority="2" operator="lessThanOrEqual">
       <formula>700</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8856,17 +9070,17 @@
     <mergeCell ref="B18:C18"/>
   </mergeCells>
   <conditionalFormatting sqref="E2:E9">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="39" priority="4" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D9">
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="lessThanOrEqual">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F9">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="lessThanOrEqual">
       <formula>30</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9083,47 +9297,59 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>85</v>
+      </c>
+      <c r="B8">
+        <v>75</v>
+      </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>38.75</v>
       </c>
       <c r="D8">
         <f>Tabela13467[[#This Row],[C]]</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E8" s="8">
         <f>Tabela13467[[#This Row],[G]]</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>30</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="D9">
         <f>Tabela13467[[#This Row],[C]]</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E9" s="8">
         <f>Tabela13467[[#This Row],[G]]</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9455,53 +9681,53 @@
     <mergeCell ref="B18:C18"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:D9">
-    <cfRule type="cellIs" dxfId="16" priority="14" operator="greaterThanOrEqual">
-      <formula>85000</formula>
+    <cfRule type="cellIs" dxfId="19" priority="14" operator="greaterThanOrEqual">
+      <formula>85</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E8">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="greaterThanOrEqual">
-      <formula>100000</formula>
+    <cfRule type="cellIs" dxfId="18" priority="13" operator="greaterThanOrEqual">
+      <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="greaterThanOrEqual">
-      <formula>70000</formula>
+    <cfRule type="cellIs" dxfId="17" priority="12" operator="greaterThanOrEqual">
+      <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="greaterThanOrEqual">
-      <formula>85000</formula>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="greaterThanOrEqual">
+      <formula>160</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:D36">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="greaterThanOrEqual">
       <formula>85000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29:E36">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="greaterThanOrEqual">
       <formula>100000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F36">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="greaterThanOrEqual">
       <formula>70000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29:G36">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="greaterThanOrEqual">
       <formula>85000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
-      <formula>100000</formula>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThanOrEqual">
+      <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThanOrEqual">
-      <formula>70000</formula>
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThanOrEqual">
+      <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
